--- a/ClassMaterial/프로젝트 기획_김현규(배경, 기술)_0311.xlsx
+++ b/ClassMaterial/프로젝트 기획_김현규(배경, 기술)_0311.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hkkim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9531AFA-3D3B-4DFD-9E08-F7EC27785B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3579F902-67E2-4BCB-80FE-A068BB14FD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,11 +59,6 @@
   </si>
   <si>
     <t>사용자 맞춤형 자동 보안 설정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>위급 상황 시 자동 경고 시스템(알림, 연락, 스마트 전력 차단 등)과 사용자 직접 조치(원격 제어)의 연동
-위험 구역 접근 거리 등 사용자 정의 값에 따라 시스템이 스스로 경고음을 발생시키거나 전력을 차단하는 등의 능동적 조치</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -105,6 +100,10 @@
       </rPr>
       <t>(정상/주의/경고/위험)</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험 구역 접근 거리 등 사용자 정의 값에 따라 시스템이 스스로 경고음을 발생시키거나 전력을 차단하는 등의 능동적 조치</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -585,7 +584,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -628,7 +627,7 @@
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
     </row>
-    <row r="8" spans="1:13" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -636,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -655,7 +654,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>

--- a/ClassMaterial/프로젝트 기획_김현규(배경, 기술)_0311.xlsx
+++ b/ClassMaterial/프로젝트 기획_김현규(배경, 기술)_0311.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hkkim\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\JavaClass\ClassMaterial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3579F902-67E2-4BCB-80FE-A068BB14FD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="주요기능" sheetId="3" r:id="rId1"/>
@@ -38,10 +37,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>영상(시각), 소리(청각), 센서(환경) 데이터를 복합 분석하여 위험 상황 발생 시 즉시 점수 반영 및 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>스마트 데이터 히스토리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -54,18 +49,39 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>위험 감지 시 브라우저에서 사용자의 버튼 조작(간식 급여, 보호자 음성 송출, 스마트 조명 제어 등)을 통해 즉각적 원격 개입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자 맞춤형 자동 보안 설정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>위험 점수 높았던 순간의 이벤트 스냅샷, 조치 이력을 타임라인으로 시각화 하여 장기적인 행동 패턴 분석 지원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
+    <t>ㅇ 영상(시각), 소리(청각), 센서(환경) 데이터를 복합 분석ㅇ 위험 상황 발생 시 즉시 점수 반영 및 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇ 위험 감지 시 브라우저에서 사용자가 버튼 조작
+ㅇ 간식 급여, 보호자 음성 송출, 스마트 조명 제어 등의 원격 조치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇ 위험 구역 접근 거리 등 사용자 정의 값에 따라 시스템이 능동적으로 조치
+ㅇ 경고음 발생, 전력 차단 등</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇ 위험 점수 높았던 순간의 이벤트 스냅샷, 조치 이력을 타임라인으로 시각화
+ㅇ 장기적인 행동 패턴 분석 지원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ㅇ </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -87,7 +103,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 및 행동 분석을 통해 수면 부족, 식사, 거름 위험구역 접근 등 이상 징후의 실시간 수치화, 직관적 위험 등급 제공</t>
+      <t xml:space="preserve"> 및 행동 분석을 통해 수면 부족, 식사 거름, 위험구역 접근 등 이상 징후의 실시간 수치화
+ㅇ 직관적인 위험 등급 제공</t>
     </r>
     <r>
       <rPr>
@@ -102,16 +119,12 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
-  <si>
-    <t>위험 구역 접근 거리 등 사용자 정의 값에 따라 시스템이 스스로 경고음을 발생시키거나 전력을 차단하는 등의 능동적 조치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +181,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -221,20 +241,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -245,6 +251,20 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,203 +567,203 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:M17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="39.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.75" customWidth="1"/>
+    <col min="3" max="3" width="48.875" customWidth="1"/>
     <col min="8" max="8" width="5.25" customWidth="1"/>
     <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:13" ht="49.5">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:13" ht="33" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:13" ht="33">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="49.5">
+      <c r="A7" s="13">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="49.5">
+      <c r="A8" s="13">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" ht="49.5">
+      <c r="A9" s="13">
         <v>5</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-    </row>
-    <row r="7" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-    </row>
-    <row r="8" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-    </row>
-    <row r="9" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-    </row>
-    <row r="17" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="6:13">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
